--- a/data/trans_bre/IP16B98-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Provincia-trans_bre.xlsx
@@ -563,7 +563,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 84,11</t>
+          <t>-33,31; 85,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,14 +616,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,77; —</t>
+          <t>-33,35; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,36</t>
+          <t>0,0; 78,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 362,17</t>
+          <t>0,0; 371,72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 64,75</t>
+          <t>-25,86; 63,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 230,59</t>
+          <t>-25,97; 257,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 16,2</t>
+          <t>-11,01; 16,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,21</t>
+          <t>-3,73; 16,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 19,87</t>
+          <t>-11,43; 20,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 21,45</t>
+          <t>-4,01; 20,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B98-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 85,95</t>
+          <t>-33,58; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,35; —</t>
+          <t>-35,32; —</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,79</t>
+          <t>0,0; 78,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 371,72</t>
+          <t>0,0; 362,17</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 63,92</t>
+          <t>-25,16; 63,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 257,75</t>
+          <t>-25,3; 236,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 16,41</t>
+          <t>-12,83; 14,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 16,81</t>
+          <t>-4,58; 16,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 20,33</t>
+          <t>-13,96; 17,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 20,64</t>
+          <t>-4,7; 20,41</t>
         </is>
       </c>
     </row>
